--- a/data/trans_orig/P32C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P32C-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2007</t>
+          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2007 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>905</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7581</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7542</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>432048</t>
+          <t>431738</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>438421</t>
+          <t>438414</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>178723</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>180606</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>612383</t>
+          <t>612055</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16747</t>
+          <t>17575</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16929</t>
+          <t>17309</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>565152</t>
+          <t>564324</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>577956</t>
+          <t>577894</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>277479</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>279511</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>844480</t>
+          <t>844100</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>857723</t>
+          <t>857413</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18912</t>
+          <t>19140</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5814</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20247</t>
+          <t>21540</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311140</t>
+          <t>310912</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>324500</t>
+          <t>324574</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127575</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129413</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>439217</t>
+          <t>437924</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>453650</t>
+          <t>453443</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21277</t>
+          <t>21210</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16409</t>
+          <t>16403</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12504</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30704</t>
+          <t>31592</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>507372</t>
+          <t>507439</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>521847</t>
+          <t>521933</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>288646</t>
+          <t>288652</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>301108</t>
+          <t>301965</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>803000</t>
+          <t>802112</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>821200</t>
+          <t>819852</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24534</t>
+          <t>25161</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49733</t>
+          <t>49639</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>17009</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31280</t>
+          <t>31509</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59731</t>
+          <t>57626</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1830185</t>
+          <t>1830279</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1855384</t>
+          <t>1854757</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>878207</t>
+          <t>877575</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>891055</t>
+          <t>891114</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2714772</t>
+          <t>2716877</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2743223</t>
+          <t>2742994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2012</t>
+          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2012 (tasa de respuesta: 99,17%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2849</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12198</t>
+          <t>12256</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13369</t>
+          <t>13655</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>412882</t>
+          <t>412824</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>422231</t>
+          <t>422647</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166939</t>
+          <t>167264</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>583676</t>
+          <t>583390</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>593830</t>
+          <t>594032</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16034</t>
+          <t>16534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16376</t>
+          <t>15973</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>575202</t>
+          <t>574702</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>587198</t>
+          <t>587288</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>291358</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>293452</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>868312</t>
+          <t>868715</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>880604</t>
+          <t>880956</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17349</t>
+          <t>18389</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18735</t>
+          <t>19009</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>441342</t>
+          <t>440302</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>453603</t>
+          <t>453464</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>202776</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>204948</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>644903</t>
+          <t>644629</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658575</t>
+          <t>658489</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9246</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27258</t>
+          <t>27406</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6143</t>
+          <t>6879</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11236</t>
+          <t>10993</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30028</t>
+          <t>29373</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>529970</t>
+          <t>529822</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>547982</t>
+          <t>547802</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>364041</t>
+          <t>363305</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>897385</t>
+          <t>898040</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>916177</t>
+          <t>916420</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29656</t>
+          <t>29063</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56954</t>
+          <t>54709</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>997</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9173</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31615</t>
+          <t>31268</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59712</t>
+          <t>59237</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1975281</t>
+          <t>1977526</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2002579</t>
+          <t>2003172</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1031376</t>
+          <t>1032149</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1039548</t>
+          <t>1039552</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3013073</t>
+          <t>3013548</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3041170</t>
+          <t>3041517</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2016</t>
+          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15433</t>
+          <t>16005</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15818</t>
+          <t>15387</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>407280</t>
+          <t>406708</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419483</t>
+          <t>419134</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>182083</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>183921</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>590816</t>
+          <t>591247</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>603549</t>
+          <t>603437</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>16767</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18239</t>
+          <t>18153</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>549521</t>
+          <t>549371</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>561958</t>
+          <t>562209</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>308518</t>
+          <t>309068</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>862524</t>
+          <t>862610</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>876134</t>
+          <t>876159</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15617</t>
+          <t>16208</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16553</t>
+          <t>15556</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>411070</t>
+          <t>410479</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>422906</t>
+          <t>422819</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>226625</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>228647</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>638782</t>
+          <t>639779</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>651322</t>
+          <t>651386</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13739</t>
+          <t>13748</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>12040</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>6871</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21399</t>
+          <t>20934</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>551959</t>
+          <t>551950</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>562759</t>
+          <t>562698</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>392626</t>
+          <t>390980</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>401063</t>
+          <t>401030</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>947319</t>
+          <t>947784</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>962401</t>
+          <t>961847</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22488</t>
+          <t>22072</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44608</t>
+          <t>45121</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,49 +6014,49 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>6210</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2095</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>12883</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
           <t>1,14%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6210</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2921</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>13756</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>36</t>
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27679</t>
+          <t>27460</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52044</t>
+          <t>51938</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1936628</t>
+          <t>1936115</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1958748</t>
+          <t>1959164</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,47 +6127,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>98,89%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1075</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1124004</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1117331</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1128119</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
           <t>98,86%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1075</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1124004</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1116458</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1127293</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,78%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3059406</t>
+          <t>3059512</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3083771</t>
+          <t>3083990</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2023</t>
+          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2023 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>571</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4992</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7727</t>
+          <t>8529</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>328030</t>
+          <t>327573</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>332990</t>
+          <t>332996</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>155105</t>
+          <t>155183</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>485938</t>
+          <t>485136</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>492224</t>
+          <t>492177</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14274</t>
+          <t>14850</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>978</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10429</t>
+          <t>9710</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18915</t>
+          <t>20050</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>462482</t>
+          <t>461906</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>473351</t>
+          <t>473177</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>191177</t>
+          <t>191896</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>200619</t>
+          <t>200628</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>659447</t>
+          <t>658312</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>672894</t>
+          <t>672243</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7923</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14080</t>
+          <t>14747</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15036</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>317425</t>
+          <t>317004</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>362017</t>
+          <t>361350</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>686409</t>
+          <t>687324</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>700600</t>
+          <t>701445</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>13430</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>803</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5447</t>
+          <t>5487</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15577</t>
+          <t>14654</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>430341</t>
+          <t>430270</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>440480</t>
+          <t>440211</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>284135</t>
+          <t>284095</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>288798</t>
+          <t>288779</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>717704</t>
+          <t>718627</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>728240</t>
+          <t>728473</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>12648</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27422</t>
+          <t>27601</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,82 +7961,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>9252</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>3393</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>18061</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>28069</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>18427</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>39892</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>9252</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>3608</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>18783</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>28069</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>19245</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>40527</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1551949</t>
+          <t>1551770</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1568189</t>
+          <t>1566723</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,82 +8074,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1193</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1018130</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1009321</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1023989</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>99,67%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>2756</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>2578684</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>2566861</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>2588326</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>98,92%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>98,47%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>99,29%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1193</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1018130</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1008599</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1023774</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,17%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2756</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>2578684</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>2566226</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>2587508</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>98,92%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P32C-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>902</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7581</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>901</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>8328</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>431738</t>
+          <t>431911</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>438414</t>
+          <t>438417</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>612055</t>
+          <t>611597</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>619021</t>
+          <t>619024</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17575</t>
+          <t>18352</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17309</t>
+          <t>17598</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>564324</t>
+          <t>563547</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>577894</t>
+          <t>577849</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>844100</t>
+          <t>843811</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>857413</t>
+          <t>857685</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19140</t>
+          <t>20976</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>5758</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21540</t>
+          <t>19292</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310912</t>
+          <t>309076</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>324574</t>
+          <t>324042</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>437924</t>
+          <t>440172</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>453443</t>
+          <t>453706</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6716</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21210</t>
+          <t>21347</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16403</t>
+          <t>16760</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13852</t>
+          <t>12819</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31592</t>
+          <t>32751</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>507439</t>
+          <t>507302</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>521933</t>
+          <t>521766</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>288652</t>
+          <t>288295</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>301965</t>
+          <t>301985</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>802112</t>
+          <t>800953</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>819852</t>
+          <t>820885</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25161</t>
+          <t>24416</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49639</t>
+          <t>48743</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17009</t>
+          <t>16168</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31509</t>
+          <t>31482</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57626</t>
+          <t>57897</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1830279</t>
+          <t>1831175</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1854757</t>
+          <t>1855502</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>877575</t>
+          <t>878416</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>891114</t>
+          <t>890882</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2716877</t>
+          <t>2716606</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2742994</t>
+          <t>2743021</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>2373</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12256</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13655</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>412824</t>
+          <t>413857</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>422647</t>
+          <t>422707</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>167264</t>
+          <t>166407</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>583390</t>
+          <t>583938</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>594032</t>
+          <t>593838</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3948</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16534</t>
+          <t>15958</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15973</t>
+          <t>16052</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>574702</t>
+          <t>575278</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>587288</t>
+          <t>587211</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>868715</t>
+          <t>868636</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>880956</t>
+          <t>880676</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18389</t>
+          <t>17861</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19009</t>
+          <t>19033</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>440302</t>
+          <t>440830</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>453464</t>
+          <t>453607</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>644629</t>
+          <t>644605</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658489</t>
+          <t>658355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27406</t>
+          <t>26168</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10993</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29373</t>
+          <t>29996</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>529822</t>
+          <t>531060</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>547802</t>
+          <t>547486</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>363305</t>
+          <t>363867</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>898040</t>
+          <t>897417</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>916420</t>
+          <t>916484</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29063</t>
+          <t>30521</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54709</t>
+          <t>56367</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,82 +4067,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>3038</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8150</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>43958</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>31979</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>58695</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>1,43%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3038</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>997</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8400</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>43958</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>31268</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>59237</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1977526</t>
+          <t>1975868</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2003172</t>
+          <t>2001714</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,82 +4180,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>98,5%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1037511</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1032399</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1039557</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>2824</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>3028827</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>3014090</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>3040806</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>98,57%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>953</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1037511</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1032149</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1039552</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2824</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>3028827</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>3013548</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>3041517</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>98,57%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16005</t>
+          <t>16522</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15387</t>
+          <t>16886</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406708</t>
+          <t>406191</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419134</t>
+          <t>419394</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>591247</t>
+          <t>589748</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>603437</t>
+          <t>603501</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16767</t>
+          <t>15772</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18153</t>
+          <t>17181</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>549371</t>
+          <t>550366</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>562209</t>
+          <t>562921</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>309068</t>
+          <t>310143</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>862610</t>
+          <t>863582</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>876159</t>
+          <t>876100</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16208</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15556</t>
+          <t>15230</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>410479</t>
+          <t>410375</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>639779</t>
+          <t>640105</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>651386</t>
+          <t>651406</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13748</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12040</t>
+          <t>11435</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20934</t>
+          <t>20336</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>551950</t>
+          <t>551586</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>562698</t>
+          <t>562711</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>390980</t>
+          <t>391585</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>401030</t>
+          <t>401035</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>947784</t>
+          <t>948382</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>961847</t>
+          <t>962607</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22072</t>
+          <t>22204</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45121</t>
+          <t>44470</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12883</t>
+          <t>12297</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27460</t>
+          <t>26676</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51938</t>
+          <t>51967</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1936115</t>
+          <t>1936766</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1959164</t>
+          <t>1959032</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1117331</t>
+          <t>1117917</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3059512</t>
+          <t>3059483</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3083990</t>
+          <t>3084774</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -6569,102 +6569,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>556</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>5984</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1318</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4695</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>3756</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1427</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>8038</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1307</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4914</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>3688</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1488</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>8529</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -6682,102 +6682,102 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>331186</t>
+          <t>351501</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>327573</t>
+          <t>347955</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>332996</t>
+          <t>353383</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>99,31%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,84%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>171764</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>168387</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>173082</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>99,24%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,29%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>523264</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>518982</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>525593</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>99,29%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>98,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,83%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>158790</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>155183</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>160097</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,93%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>489977</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>485136</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>492177</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>333567</t>
+          <t>353939</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>333567</t>
+          <t>353939</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>333567</t>
+          <t>353939</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>160097</t>
+          <t>173082</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>160097</t>
+          <t>173082</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>160097</t>
+          <t>173082</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>493665</t>
+          <t>527020</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>493665</t>
+          <t>527020</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>493665</t>
+          <t>527020</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>7380</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14850</t>
+          <t>13281</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>9486</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>10697</t>
+          <t>10911</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20050</t>
+          <t>19498</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>469468</t>
+          <t>493343</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>461906</t>
+          <t>487442</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>473177</t>
+          <t>497675</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>198197</t>
+          <t>220356</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>191896</t>
+          <t>214401</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>200628</t>
+          <t>222867</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>667665</t>
+          <t>713700</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>658312</t>
+          <t>705113</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>672243</t>
+          <t>718256</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>476756</t>
+          <t>500723</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>476756</t>
+          <t>500723</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>476756</t>
+          <t>500723</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>201606</t>
+          <t>223887</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>201606</t>
+          <t>223887</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>201606</t>
+          <t>223887</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>678362</t>
+          <t>724611</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>678362</t>
+          <t>724611</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>678362</t>
+          <t>724611</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14747</t>
+          <t>10926</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>14752</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -7368,27 +7368,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>323098</t>
+          <t>357881</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>317004</t>
+          <t>352232</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>325348</t>
+          <t>360183</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7403,27 +7403,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>373869</t>
+          <t>198910</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>361350</t>
+          <t>190208</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>376097</t>
+          <t>201134</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>696968</t>
+          <t>556791</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>687324</t>
+          <t>546565</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>701445</t>
+          <t>560175</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>325348</t>
+          <t>360183</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>325348</t>
+          <t>360183</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>325348</t>
+          <t>360183</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>376097</t>
+          <t>201134</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>376097</t>
+          <t>201134</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>376097</t>
+          <t>201134</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>701445</t>
+          <t>561317</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>701445</t>
+          <t>561317</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>701445</t>
+          <t>561317</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6898</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13430</t>
+          <t>13810</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2309</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>14250</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>12308</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14654</t>
+          <t>22560</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>436802</t>
+          <t>457901</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>430270</t>
+          <t>451854</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>440211</t>
+          <t>462254</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>287273</t>
+          <t>304085</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>284095</t>
+          <t>294380</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>288779</t>
+          <t>307426</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>724075</t>
+          <t>761986</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>718627</t>
+          <t>751734</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>728473</t>
+          <t>767573</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>443700</t>
+          <t>465664</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>443700</t>
+          <t>465664</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>443700</t>
+          <t>465664</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>289582</t>
+          <t>308630</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>289582</t>
+          <t>308630</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>289582</t>
+          <t>308630</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>733281</t>
+          <t>774294</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>733281</t>
+          <t>774294</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>733281</t>
+          <t>774294</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18817</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12648</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27601</t>
+          <t>29087</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,67 +7976,67 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18061</t>
+          <t>23533</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>31502</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>21866</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>45461</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>1,76%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>28069</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>18427</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>39892</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1560554</t>
+          <t>1660625</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1551770</t>
+          <t>1651422</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1566723</t>
+          <t>1667328</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,67 +8089,67 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1018130</t>
+          <t>895115</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1009321</t>
+          <t>883200</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1023989</t>
+          <t>901687</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>99,44%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>2756</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>2555740</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>2541781</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>2565376</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>98,78%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>98,24%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,67%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2756</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>2578684</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>2566861</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>2588326</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>98,92%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>98,47%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1579371</t>
+          <t>1680509</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1579371</t>
+          <t>1680509</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1579371</t>
+          <t>1680509</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1027382</t>
+          <t>906733</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1027382</t>
+          <t>906733</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1027382</t>
+          <t>906733</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2606753</t>
+          <t>2587242</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2606753</t>
+          <t>2587242</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2606753</t>
+          <t>2587242</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
